--- a/ig/UniformiserIndentation/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/UniformiserIndentation/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T13:29:16+00:00</t>
+    <t>2024-02-13T13:31:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/UniformiserIndentation/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/UniformiserIndentation/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T13:31:50+00:00</t>
+    <t>2024-02-14T10:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/UniformiserIndentation/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/UniformiserIndentation/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-14T10:03:30+00:00</t>
+    <t>2024-02-15T10:22:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
